--- a/12_ai-governance-operating-model/exercises/solution/ai_governance_core.xlsx
+++ b/12_ai-governance-operating-model/exercises/solution/ai_governance_core.xlsx
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Govern 6.2 — Mechanisms exist to communicate to relevant stakeholders the impacts of AI.</t>
+          <t>Govern 4.2 — Organizational teams document the risks and potential impacts of the AI technology they design, develop, deploy, evaluate, and use, and they communicate about the impacts more broadly.</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." Where the Govern Crosswalk maps internal reporting cadence to Govern 6.1 or stakeholder communication to Govern 6.2, the 6.x family's primary scope is third-party and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. The 6.x mappings used here capture the third-party / external-vendor reporting view of those controls.</t>
+          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." Where the Govern Crosswalk maps internal reporting cadence to Govern 6.1 or stakeholder communication to Govern 6.2, the 6.x family's primary scope is third-party and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. Rows that concern third-party / external-vendor contingencies map to the 6.x family; the internal reporting-cadence row maps to Govern 4.2 (impact communication).</t>
         </is>
       </c>
     </row>

--- a/12_ai-governance-operating-model/exercises/solution/ai_governance_core.xlsx
+++ b/12_ai-governance-operating-model/exercises/solution/ai_governance_core.xlsx
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Govern 2.2 — Personnel and partners are trained to perform AI-risk duties.</t>
+          <t>Govern 2.3 — Executive leadership takes responsibility for decisions about risks associated with AI system development and deployment.</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>A.10.2 Suppliers — assessment, due diligence, and ongoing oversight of AI providers.</t>
+          <t>A.10.3 Suppliers — assessment, due diligence, and ongoing oversight of AI providers.</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Govern 1.4 — Processes are in place to evaluate the effectiveness of AI risk management.</t>
+          <t>Govern 1.5 — Ongoing monitoring and periodic review of the risk management process and its outcomes are planned.</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -1788,7 +1788,7 @@
       <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Stress-testing the design against named failure modes is the form of "evaluating the effectiveness" — it produces written evidence the design has been challenged.
-Reasoning: without the stress-test, Govern 1.4 is unfalsifiable. The stress-test sheet is the artifact that satisfies it.</t>
+Reasoning: without the stress-test, Govern 1.5 is unfalsifiable. The stress-test sheet is the artifact that satisfies it.</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B2" s="25" t="inlineStr">
         <is>
-          <t>In ISO/IEC 42001:2023 Annex A, the supplier-management control sits at A.10.3 ("Suppliers") within Clause A.10 (Third-party and customer relationships). A.10.2 in the same clause is "Allocating responsibilities" and addresses how the organization allocates responsibilities for the AI system across its lifecycle. Where the Govern Crosswalk references A.10.2 in a vendor-onboarding context, the Suppliers control (A.10.3) is the closer ISO 42001 anchor; both controls can apply when supplier onboarding also involves dividing responsibilities across teams. Reference: ISMS.online A.10.3 Suppliers.</t>
+          <t>In ISO/IEC 42001:2023 Annex A, the supplier-management control sits at A.10.3 ("Suppliers") within Clause A.10 (Third-party and customer relationships). A.10.2 in the same clause is "Allocating responsibilities" and addresses how the organization allocates responsibilities for the AI system across its lifecycle. The Crosswalk's vendor-onboarding row therefore anchors to A.10.3 (Suppliers); A.10.2 can also apply where supplier onboarding involves dividing responsibilities across teams. Reference: ISMS.online A.10.3 Suppliers.</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." Where the Govern Crosswalk maps internal reporting cadence to Govern 6.1 or stakeholder communication to Govern 6.2, the 6.x family's primary scope is third-party and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. Rows that concern third-party / external-vendor contingencies map to the 6.x family; the internal reporting-cadence row maps to Govern 4.2 (impact communication).</t>
+          <t>NIST AI 100-1 Govern subcategory 6.1 = "Policies and procedures address AI risks from third-party entities." Govern 6.2 = "Contingency processes handle failures or incidents in third-party data or high-risk AI systems." The 6.x family's primary scope is third-party risk and contingency; broader stakeholder communication aligns with the Govern 5.x family ("Processes are in place for robust engagement with relevant AI actors") and reporting cadence within the organization aligns with Govern 1.x and 4.x. Rows that concern third-party / external-vendor contingencies map to the 6.x family; the internal reporting-cadence row maps to Govern 4.2 (impact communication).</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Govern 1.4 = "Risk management process and outcomes are established through transparent policies, procedures, and other controls." Govern 1.5 = "Ongoing monitoring and periodic review of the risk management process and its outcomes are planned." Where the Crosswalk paraphrases Govern 1.4 as "evaluating effectiveness of AI risk management," the periodic-review framing aligns more precisely with Govern 1.5; both subcategories together cover policy + ongoing review.</t>
+          <t>Govern 1.4 = "Risk management process and outcomes are established through transparent policies, procedures, and other controls." Govern 1.5 = "Ongoing monitoring and periodic review of the risk management process and its outcomes are planned." The Crosswalk's failure-mode stress-test row therefore anchors to Govern 1.5 (periodic review of the risk-management process); 1.4 and 1.5 together cover policy plus ongoing review.</t>
         </is>
       </c>
     </row>
